--- a/output/pdf_financials_xlsx/NTB.xlsx
+++ b/output/pdf_financials_xlsx/NTB.xlsx
@@ -1309,13 +1309,13 @@
         <v>-0.253549</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.302676</v>
+        <v>-0.302676</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.347233</v>
@@ -1625,13 +1625,13 @@
         <v>-0.253549</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.302676</v>
+        <v>-0.302676</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.347233</v>
@@ -1808,13 +1808,13 @@
         <v>-0.253549</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.302676</v>
+        <v>-0.302676</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.347233</v>
@@ -2092,13 +2092,13 @@
         <v>-0.253549</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.302676</v>
+        <v>-0.302676</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.347233</v>
@@ -2214,13 +2214,13 @@
         <v>-0.253549</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.302676</v>
+        <v>-0.302676</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.347233</v>
@@ -2372,13 +2372,13 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -6204,43 +6204,43 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="93">
@@ -6573,10 +6573,10 @@
         <v>-0.302676</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.347233</v>
@@ -7738,7 +7738,7 @@
         <v>0.014403</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.020472</v>
+        <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -7747,28 +7747,28 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.005835</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.00185</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.116042</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.022531</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>0</v>
@@ -10172,7 +10172,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -17278,7 +17282,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -20120,7 +20128,11 @@
           <t>Write-off of exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -35196,10 +35208,10 @@
         </is>
       </c>
       <c r="I256" s="5" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="J256" s="5" t="n">
-        <v>0.347233</v>
+        <v>-0.347233</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -35833,10 +35845,10 @@
         </is>
       </c>
       <c r="H262" s="5" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>0.349336</v>
+        <v>-0.349336</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -36256,10 +36268,10 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>0.302676</v>
+        <v>-0.302676</v>
       </c>
       <c r="H266" s="5" t="n">
-        <v>0.318999</v>
+        <v>-0.318999</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NTB.xlsx
+++ b/output/pdf_financials_xlsx/NTB.xlsx
@@ -958,37 +958,37 @@
         <v>0.113038</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.112789</v>
+        <v>0.361519</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.113426</v>
+        <v>0.414742</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.113553</v>
+        <v>0.264684</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.187447</v>
+        <v>0.28073</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.17614</v>
+        <v>0.380483</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.161327</v>
+        <v>0.233499</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.146043</v>
+        <v>0.258926</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.147042</v>
+        <v>0.249437</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.148774</v>
+        <v>0.225239</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.154696</v>
+        <v>0.208066</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.152305</v>
+        <v>0.509482</v>
       </c>
     </row>
     <row r="11">
@@ -1019,37 +1019,37 @@
         <v>-0.113038</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.112789</v>
+        <v>-0.361519</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.113426</v>
+        <v>-0.414742</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.113553</v>
+        <v>-0.264684</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.187447</v>
+        <v>-0.28073</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.17614</v>
+        <v>-0.380483</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.161327</v>
+        <v>-0.233499</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.146043</v>
+        <v>-0.258926</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.147042</v>
+        <v>-0.249437</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.148774</v>
+        <v>-0.225239</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.154696</v>
+        <v>-0.208066</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.152305</v>
+        <v>-0.509482</v>
       </c>
     </row>
     <row r="12">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002442</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001603</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001024</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>5.6e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002326</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000168</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2086,22 +2086,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.26862</v>
+        <v>-0.271062</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.253549</v>
+        <v>-0.255152</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.302676</v>
+        <v>-0.301652</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.318999</v>
+        <v>-0.319055</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.349336</v>
+        <v>-0.351662</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.347233</v>
+        <v>-0.347401</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.307477</v>
@@ -2208,22 +2208,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.26862</v>
+        <v>-0.271062</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.253549</v>
+        <v>-0.255152</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.302676</v>
+        <v>-0.301652</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.318999</v>
+        <v>-0.319055</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.349336</v>
+        <v>-0.351662</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.347233</v>
+        <v>-0.347401</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.307225</v>
@@ -2549,40 +2549,40 @@
         <v>0.005165</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.007055</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003211</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000226</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.007195</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.007334</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.194037</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001404</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.126343</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.003798</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.022568</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.005041</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.003565</v>
       </c>
     </row>
     <row r="35">
@@ -2671,40 +2671,40 @@
         <v>0.005165</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.007055</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003211</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000226</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.007195</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.007334</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.194037</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.001404</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.126343</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.003798</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.022568</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.005041</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.003565</v>
       </c>
     </row>
     <row r="37">
@@ -3403,40 +3403,40 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.007055</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.003211</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.025226</v>
+        <v>0.025</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.032195</v>
+        <v>0.025</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.032334</v>
+        <v>0.025</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.219768</v>
+        <v>0.025731</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.027135</v>
+        <v>0.025731</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.157074</v>
+        <v>0.030731</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.032029</v>
+        <v>0.028231</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.048299</v>
+        <v>0.025731</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.030772</v>
+        <v>0.025731</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.029296</v>
+        <v>0.025731</v>
       </c>
     </row>
     <row r="49">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -26831,10 +26831,10 @@
         </is>
       </c>
       <c r="L174" s="5" t="n">
-        <v>-0.361519</v>
+        <v>0.361519</v>
       </c>
       <c r="M174" s="5" t="n">
-        <v>-0.414742</v>
+        <v>0.414742</v>
       </c>
       <c r="N174" s="5" t="n">
         <v>0.264684</v>
@@ -26976,7 +26976,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -28898,7 +28898,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -33130,7 +33130,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -38558,7 +38558,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" s="5" t="n">

--- a/output/pdf_financials_xlsx/NTB.xlsx
+++ b/output/pdf_financials_xlsx/NTB.xlsx
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.063282</v>
+        <v>0.09628200000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.059537</v>
+        <v>0.09253699999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.060838</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.123651</v>
+        <v>0.156651</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.116141</v>
+        <v>0.149141</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.118148</v>
@@ -3692,19 +3692,19 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.00036</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0.000252</v>
@@ -4406,19 +4406,19 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.027631</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.056021</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.269298</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.444691</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.120629</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0</v>
@@ -4656,10 +4656,10 @@
         <v>0.056021</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.269298</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.444691</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.120629</v>
@@ -4717,10 +4717,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>0.0665</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0</v>
+        <v>0.057183</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
@@ -4839,10 +4839,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.0665</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.057183</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
@@ -5421,15 +5421,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>0.220389144260437</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>-0.3089720383628259</v>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
@@ -5941,19 +5937,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>6.232331</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>7.033331</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>7.033331</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>7.033331</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>7.499331</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>7.919331</v>
@@ -6189,19 +6185,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.0075</v>
@@ -12502,7 +12498,11 @@
           <t>Equipment – Note 7</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12906,7 +12906,11 @@
           <t>Trades and other payables – Note 12 $</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13004,7 +13008,11 @@
           <t>Loans payable – Note 13</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13210,7 +13218,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13312,7 +13324,11 @@
           <t>Contributed surplus – Note 8</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13838,7 +13854,11 @@
           <t>Loans payable - Note 13</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -13944,7 +13964,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14046,7 +14070,11 @@
           <t>Contributed surplus – Note 8</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -14672,7 +14700,11 @@
           <t>Equipment - Note 3</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -14986,7 +15018,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>6.232331</v>
       </c>
@@ -15088,7 +15124,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>0.0075</v>
       </c>
@@ -15510,7 +15550,11 @@
           <t>Equipment – Note 3</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>0.00036</v>
       </c>
@@ -15614,7 +15658,11 @@
           <t>Mineral properties – Note 4</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -36570,7 +36618,11 @@
           <t>Administration fees – Note 5</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="n">
         <v>0.033</v>
       </c>

--- a/output/pdf_financials_xlsx/NTB.xlsx
+++ b/output/pdf_financials_xlsx/NTB.xlsx
@@ -754,40 +754,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.09628200000000001</v>
+        <v>0.102282</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.09253699999999999</v>
+        <v>0.104537</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.060838</v>
+        <v>0.075838</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.061516</v>
+        <v>0.078016</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.070033</v>
+        <v>0.086533</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.116469</v>
+        <v>0.131469</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.113038</v>
+        <v>0.128038</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.112789</v>
+        <v>0.127789</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.113426</v>
+        <v>0.117926</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.113553</v>
+        <v>0.118053</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.187447</v>
+        <v>0.191947</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.17614</v>
+        <v>0.18139</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.161327</v>
@@ -805,7 +805,7 @@
         <v>0.154696</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.152305</v>
+        <v>0.156805</v>
       </c>
     </row>
     <row r="8">
@@ -937,25 +937,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.156651</v>
+        <v>0.162651</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.149141</v>
+        <v>0.161141</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.118148</v>
+        <v>0.133148</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.12035</v>
+        <v>0.13685</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.133949</v>
+        <v>0.150449</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.181303</v>
+        <v>0.196303</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.113038</v>
+        <v>0.128038</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.361519</v>
@@ -1013,10 +1013,10 @@
         <v>0.347034</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.181303</v>
+        <v>-0.196303</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.113038</v>
+        <v>-0.128038</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.361519</v>
@@ -4430,25 +4430,25 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>1.362367</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>1.548739</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.282344</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>1.320449</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>1.351332</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>1.427245</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.054072</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -6682,13 +6682,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.00049</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.002721</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.016934</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -6987,13 +6987,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>0.00049</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.036467</v>
+        <v>-0.033746</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.02839</v>
+        <v>0.011456</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.213277</v>
@@ -23160,7 +23160,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -24746,7 +24750,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E154" s="5" t="n">
         <v>0.00049</v>
       </c>
@@ -25996,7 +26004,11 @@
           <t>Director’s fees (Note 5)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -30960,7 +30972,11 @@
           <t>Directors’ fees (Note 6)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -31374,7 +31390,11 @@
           <t>Directors’ fees (Note 5)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31998,7 +32018,11 @@
           <t>Directors’ fees (Note 4)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -33894,7 +33918,11 @@
           <t>Directors’ fees – Note 12</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -37146,7 +37174,11 @@
           <t>Directors fees – Note 5</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E274" s="5" t="n">
         <v>0.006</v>
       </c>
